--- a/Team-Data/2012-13/12-31-2012-13.xlsx
+++ b/Team-Data/2012-13/12-31-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.655</v>
+        <v>0.679</v>
       </c>
       <c r="H2" t="n">
         <v>48.7</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.456</v>
       </c>
       <c r="L2" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>23.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.379</v>
+        <v>0.374</v>
       </c>
       <c r="O2" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="P2" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.711</v>
+        <v>0.709</v>
       </c>
       <c r="R2" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="S2" t="n">
         <v>30.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U2" t="n">
         <v>23.2</v>
@@ -718,73 +785,73 @@
         <v>14.7</v>
       </c>
       <c r="W2" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
       </c>
       <c r="AF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG2" t="n">
         <v>7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>8</v>
       </c>
       <c r="AH2" t="n">
         <v>6</v>
       </c>
       <c r="AI2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
       </c>
       <c r="AR2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -796,10 +863,10 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -808,13 +875,13 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
@@ -951,10 +1018,10 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -1025,67 +1092,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.516</v>
+        <v>0.533</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="J4" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.339</v>
+        <v>0.342</v>
       </c>
       <c r="O4" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P4" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R4" t="n">
         <v>12.3</v>
       </c>
       <c r="S4" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="T4" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1</v>
@@ -1094,28 +1161,28 @@
         <v>18.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>94.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="n">
         <v>12</v>
       </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>16</v>
-      </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,7 +1191,7 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1133,52 +1200,52 @@
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW4" t="n">
         <v>26</v>
       </c>
-      <c r="AV4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25</v>
-      </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -1207,85 +1274,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.258</v>
+        <v>0.233</v>
       </c>
       <c r="H5" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J5" t="n">
-        <v>82.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="N5" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O5" t="n">
         <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.74</v>
+        <v>0.749</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="T5" t="n">
-        <v>41.9</v>
+        <v>41.5</v>
       </c>
       <c r="U5" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
         <v>19.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.4</v>
+        <v>-9</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1303,43 +1370,43 @@
         <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>22</v>
@@ -1351,10 +1418,10 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -1389,106 +1456,106 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
         <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.552</v>
+        <v>0.571</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J6" t="n">
-        <v>80.5</v>
+        <v>80</v>
       </c>
       <c r="K6" t="n">
-        <v>0.435</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>4.5</v>
       </c>
       <c r="M6" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.345</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.798</v>
+        <v>0.804</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S6" t="n">
         <v>31.3</v>
       </c>
       <c r="T6" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U6" t="n">
         <v>22.5</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>5.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
         <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.3</v>
+        <v>92.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>2</v>
@@ -1515,16 +1582,16 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
         <v>17</v>
@@ -1533,7 +1600,7 @@
         <v>18</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
@@ -1542,7 +1609,7 @@
         <v>27</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>30</v>
@@ -1661,7 +1728,7 @@
         <v>29</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>24</v>
@@ -1679,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1688,13 +1755,13 @@
         <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
         <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT7" t="n">
         <v>16</v>
@@ -1703,10 +1770,10 @@
         <v>30</v>
       </c>
       <c r="AV7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1718,7 +1785,7 @@
         <v>29</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>24</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>-4.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
@@ -1864,7 +1931,7 @@
         <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
         <v>16</v>
@@ -1879,13 +1946,13 @@
         <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU8" t="n">
         <v>16</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2080,19 @@
         <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2037,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM9" t="n">
         <v>20</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2082,13 +2149,13 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
         <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2228,10 +2295,10 @@
         <v>6</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>27</v>
@@ -2240,19 +2307,19 @@
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV10" t="n">
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
         <v>14</v>
@@ -2267,7 +2334,7 @@
         <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2410,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>17</v>
@@ -2428,10 +2495,10 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2452,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -2481,64 +2548,64 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.548</v>
+        <v>0.533</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.455</v>
+        <v>0.452</v>
       </c>
       <c r="L12" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.362</v>
+        <v>0.355</v>
       </c>
       <c r="O12" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
         <v>0.768</v>
       </c>
       <c r="R12" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>4.2</v>
@@ -2547,22 +2614,22 @@
         <v>6.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.8</v>
+        <v>105.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -2571,7 +2638,7 @@
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2589,13 +2656,13 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
         <v>13</v>
@@ -2607,16 +2674,16 @@
         <v>7</v>
       </c>
       <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
         <v>8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
         <v>26</v>
@@ -2625,16 +2692,16 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -2663,64 +2730,64 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.581</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
-        <v>80.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.349</v>
+        <v>0.343</v>
       </c>
       <c r="O13" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="R13" t="n">
         <v>12.4</v>
       </c>
       <c r="S13" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="U13" t="n">
         <v>19.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X13" t="n">
         <v>7</v>
@@ -2735,43 +2802,43 @@
         <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>9</v>
       </c>
       <c r="AF13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="n">
         <v>20</v>
@@ -2780,7 +2847,7 @@
         <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
         <v>9</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2810,13 +2877,13 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>28</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>10.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2971,7 +3038,7 @@
         <v>18</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2992,7 +3059,7 @@
         <v>26</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3159,7 +3226,7 @@
         <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3171,13 +3238,13 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
         <v>7</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
         <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.679</v>
+        <v>0.704</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J16" t="n">
         <v>83.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P16" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="R16" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T16" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
         <v>9.4</v>
@@ -3272,43 +3339,43 @@
         <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z16" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="AA16" t="n">
         <v>20.2</v>
       </c>
-      <c r="AA16" t="n">
-        <v>20.1</v>
-      </c>
       <c r="AB16" t="n">
-        <v>94.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
         <v>7</v>
       </c>
       <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
         <v>5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>6</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>9</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
         <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>3</v>
@@ -3332,16 +3399,16 @@
         <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3359,10 +3426,10 @@
         <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -3391,61 +3458,61 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.724</v>
+        <v>0.714</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J17" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.493</v>
+        <v>0.494</v>
       </c>
       <c r="L17" t="n">
         <v>8.6</v>
       </c>
       <c r="M17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="O17" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R17" t="n">
         <v>8.1</v>
       </c>
       <c r="S17" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="T17" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="U17" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>8</v>
@@ -3457,22 +3524,22 @@
         <v>3.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>103</v>
+        <v>102.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3481,7 +3548,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3499,13 +3566,13 @@
         <v>10</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
@@ -3514,7 +3581,7 @@
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
         <v>29</v>
@@ -3523,10 +3590,10 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>23</v>
@@ -3535,16 +3602,16 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>-0.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
@@ -3678,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="AM18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>27</v>
@@ -3690,7 +3757,7 @@
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
@@ -3705,10 +3772,10 @@
         <v>15</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3726,7 +3793,7 @@
         <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>1.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>23</v>
@@ -3875,7 +3942,7 @@
         <v>25</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>8</v>
@@ -3884,13 +3951,13 @@
         <v>2</v>
       </c>
       <c r="AU19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
         <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -3908,7 +3975,7 @@
         <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-5.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
         <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
         <v>27</v>
@@ -4045,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
@@ -4060,19 +4127,19 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
         <v>25</v>
       </c>
       <c r="AU20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV20" t="n">
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -4197,28 +4264,28 @@
         <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
       </c>
       <c r="AF21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ21" t="n">
         <v>8</v>
       </c>
       <c r="AK21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4236,10 +4303,10 @@
         <v>24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
         <v>25</v>
@@ -4248,7 +4315,7 @@
         <v>28</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4266,7 +4333,7 @@
         <v>5</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -4301,52 +4368,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8</v>
+        <v>0.793</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L22" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M22" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="O22" t="n">
         <v>23.3</v>
       </c>
       <c r="P22" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.847</v>
+        <v>0.846</v>
       </c>
       <c r="R22" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S22" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T22" t="n">
         <v>43.4</v>
@@ -4355,10 +4422,10 @@
         <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
         <v>7.6</v>
@@ -4367,19 +4434,19 @@
         <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.9</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4394,7 +4461,7 @@
         <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4406,10 +4473,10 @@
         <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,16 +4494,16 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW22" t="n">
         <v>13</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4445,10 +4512,10 @@
         <v>2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.387</v>
+        <v>0.4</v>
       </c>
       <c r="H23" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M23" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O23" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="P23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R23" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="S23" t="n">
         <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U23" t="n">
         <v>22.7</v>
       </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
         <v>6</v>
@@ -4546,22 +4613,22 @@
         <v>4.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA23" t="n">
         <v>16.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.3</v>
+        <v>92.8</v>
       </c>
       <c r="AC23" t="n">
         <v>-2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
@@ -4573,25 +4640,25 @@
         <v>21</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
         <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4603,22 +4670,22 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU23" t="n">
         <v>6</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
@@ -4627,13 +4694,13 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
@@ -4755,7 +4822,7 @@
         <v>20</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>15</v>
@@ -4764,16 +4831,16 @@
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>22</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>29</v>
@@ -4803,19 +4870,19 @@
         <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
         <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
         <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>0.344</v>
+        <v>0.355</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
@@ -4865,7 +4932,7 @@
         <v>38.3</v>
       </c>
       <c r="J25" t="n">
-        <v>85.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.449</v>
@@ -4874,7 +4941,7 @@
         <v>6.3</v>
       </c>
       <c r="M25" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N25" t="n">
         <v>0.337</v>
@@ -4883,58 +4950,58 @@
         <v>14.5</v>
       </c>
       <c r="P25" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R25" t="n">
         <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T25" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="U25" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V25" t="n">
         <v>13.4</v>
       </c>
       <c r="W25" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X25" t="n">
         <v>5.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z25" t="n">
         <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB25" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.1</v>
+        <v>-3.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
         <v>16</v>
@@ -4946,13 +5013,13 @@
         <v>2</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
         <v>20</v>
       </c>
       <c r="AM25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN25" t="n">
         <v>26</v>
@@ -4964,13 +5031,13 @@
         <v>27</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>19</v>
       </c>
       <c r="AS25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -4982,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -4991,7 +5058,7 @@
         <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
         <v>15</v>
@@ -5116,7 +5183,7 @@
         <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
@@ -5125,10 +5192,10 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5155,7 +5222,7 @@
         <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
@@ -5164,16 +5231,16 @@
         <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
         <v>26</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -5289,28 +5356,28 @@
         <v>-5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
         <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5358,7 +5425,7 @@
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -5393,55 +5460,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.758</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J28" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.484</v>
       </c>
       <c r="L28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M28" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.793</v>
+        <v>0.794</v>
       </c>
       <c r="R28" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U28" t="n">
         <v>25.5</v>
@@ -5456,7 +5523,7 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="n">
         <v>17.5</v>
@@ -5465,16 +5532,16 @@
         <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.5</v>
+        <v>105.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
         <v>3</v>
@@ -5489,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5504,10 +5571,10 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5540,10 +5607,10 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5671,7 +5738,7 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
@@ -5683,19 +5750,19 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
         <v>8</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
         <v>22</v>
@@ -5710,7 +5777,7 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
@@ -5847,19 +5914,19 @@
         <v>18</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>18</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>19</v>
       </c>
       <c r="AK30" t="n">
         <v>15</v>
       </c>
       <c r="AL30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
@@ -5880,7 +5947,7 @@
         <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6035,7 +6102,7 @@
         <v>30</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6053,7 +6120,7 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ31" t="n">
         <v>16</v>
@@ -6071,7 +6138,7 @@
         <v>23</v>
       </c>
       <c r="AV31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>21</v>
@@ -6083,7 +6150,7 @@
         <v>14</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-31-2012-13</t>
+          <t>2012-12-31</t>
         </is>
       </c>
     </row>
